--- a/Documentazione/CHIEDERE LUNEDI.xlsx
+++ b/Documentazione/CHIEDERE LUNEDI.xlsx
@@ -9,10 +9,12 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
+    <sheet name="MASCHERA ELENA1" sheetId="2" r:id="rId2"/>
+    <sheet name="MASCHERA ELENA2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -23,8 +25,102 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Lenovo</author>
+  </authors>
+  <commentList>
+    <comment ref="A28" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>okora produci un documento che deve essere una linea guida da affidare adunosviluppatore alle prime armi , per realizzare l'intero process perun nuovo madatrio
+serviranno 2 documenti un o con la logica , la teoria, uno deve oprima caopire cosa deve fare e quali servizi,classi,ernttà sono coinvolte e in che ordine deve essere uasorta di mappa che gli speia cosa deve fare prma di inizare a scivere codice
+poi mi servirà un secondo doecumento piùdettagliato che spieghi il codice e come deuplicare uikl tuytto per un nuovo mandatario , rispettando u n flusso logico, cjhhe glipermnetta di apprendere e di essere autonomo
+inizioamo con il primo documento
+Mi dispiace, ma al momento ho difficoltà a rispondere alle richieste. Riprova tra un po'.—
+come mai?
+Mi dispiace, ma al momento ho difficoltà a rispondere alle richieste. Riprova tra un po'.—
+Oggi
+co sei
+Perfetto Denis — ora che tutto il flusso è stabile, posso costruire il primo documento:
+una linea guida teorica, una mappa concettuale, un documento di orientamento per uno sviluppatore junior che deve creare l’intero processo di importazione per un nuovo mandatario.
+Questo documento NON contiene codice.
+Serve a far capire cosa deve fare, in che ordine, quali classi sono coinvolte, perché, e come ragiona il sistema.
+È il documento che un junior deve leggere prima ancora di aprire Visual Studio.</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Lenovo</author>
+  </authors>
+  <commentList>
+    <comment ref="N45" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Prompt per la generazione del codice
+Oggetto: Creazione di una Dashboard di Riepilogo in ASP.NET MVC (C#) con stile Excel.
+Contesto: Devo sviluppare una vista in ASP.NET MVC che replichi un layout di rendicontazione provvigioni. Il design deve essere pulito, con bordi definiti e una struttura a griglia simile a un foglio Excel.
+Requisiti del Layout:
+Sidebar di Filtro (Sinistra): Una colonna stretta contenente label e DropDownList per "ANNO", "MESE" e "MANDATARIO". Deve occupare circa il 20% della larghezza.
+Area Contenuti (Destra): Divisa in due macro-sezioni verticali:
+Sezione Superiore: Titolo "RIEPILOGO TOTALI CLIENTI". Contiene due tabelle affiancate (es. "PAGAMENTO 60GG" e un'altra categoria).
+Sezione Inferiore: Titolo "RIEPILOGO TOTALI AGENTI". Contiene due tabelle affiancate simili a quelle sopra, ma con una colonna aggiuntiva "Comm. Agente".
+Struttura Tabelle:
+Ogni tabella deve avere le colonne: CLIENTE, KG, IMPORTO (e "Comm.Agente" dove previsto).
+Deve esserci una riga "TOTALE" in grassetto alla fine di ogni tabella.
+Sotto ogni tabella, un pulsante "Esporta File / STAMPA" allineato a destra.
+Stile CSS:
+Usa bordi neri sottili per simulare le celle di Excel.
+Intestazioni delle tabelle con testo centrato e font leggermente più grande.
+Layout responsive (usa Bootstrap row e col o CSS Grid).
+Dati: Fornisci il codice della View (.cshtml) utilizzando un approccio con un ViewModel fittizio o liste di oggetti semplici per popolare le righe.
+Consigli Tecnici per l'implementazione
+Se stai sviluppando questa maschera, ecco come ti suggerisco di strutturarla a livello logico:
+Il ViewModel: Crea un DashboardViewModel che contenga le liste per i dropdown e quattro liste separate (o una collezione raggruppata) per i dati delle quattro tabelle che vediamo nell'immagine.
+Gestione Layout: Nell'immagine le tabelle sono "incastrate" in celle precise. In HTML, ti conviene usare due &lt;div&gt; con classe col-md-6 (in Bootstrap) dentro una riga per la sezione Clienti, e ripetere la struttura per la sezione Agenti.
+I Pulsanti di Stampa: Per la funzione "Esporta/Stampa", ti consiglio di usare una libreria come jsPDF o AutoTable se vuoi generare il PDF direttamente dal client, oppure puntare a una action nel controller che restituisca un FileContentResult (Excel/PDF).
+Ti piacerebbe che iniziassi io stesso a scriverti una prima bozza del codice HTML/CSS basata su questo prompt?
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="56">
   <si>
     <t>Riepilogo finale (chiaro e utile)</t>
   </si>
@@ -87,13 +183,118 @@
   </si>
   <si>
     <t>alcuni li calcolo  e non li possono modificare (doifferenza)ed altri li rendo editabili su richiesta</t>
+  </si>
+  <si>
+    <t>in un secondo momento per ora solo pdf cortesia</t>
+  </si>
+  <si>
+    <t>Creare Maschera ad HoC vedi Foglio Machera</t>
+  </si>
+  <si>
+    <t>Creare Maschera 2 ad HoC vedi Foglio Machera</t>
+  </si>
+  <si>
+    <t>ANNO</t>
+  </si>
+  <si>
+    <t>DROPDOWN ANNI</t>
+  </si>
+  <si>
+    <t>MESE</t>
+  </si>
+  <si>
+    <t>DROPDOWN MESI</t>
+  </si>
+  <si>
+    <t>MANDATARIO</t>
+  </si>
+  <si>
+    <t>DROPDOWN Mandatari</t>
+  </si>
+  <si>
+    <t>RIEPILOGO TOTALI CLIENTI</t>
+  </si>
+  <si>
+    <t>PAGAMENTO 60GG</t>
+  </si>
+  <si>
+    <t>CLIENTE</t>
+  </si>
+  <si>
+    <t>KG</t>
+  </si>
+  <si>
+    <t>IMPORTO</t>
+  </si>
+  <si>
+    <t>Cts</t>
+  </si>
+  <si>
+    <t>Tbg</t>
+  </si>
+  <si>
+    <t>Pat</t>
+  </si>
+  <si>
+    <t>TOTALE</t>
+  </si>
+  <si>
+    <t>Esporta File</t>
+  </si>
+  <si>
+    <t>STAMPA</t>
+  </si>
+  <si>
+    <t>PROMPT</t>
+  </si>
+  <si>
+    <t>PAGAMENTO 90GG</t>
+  </si>
+  <si>
+    <t>TOTALE KG</t>
+  </si>
+  <si>
+    <t>TOT COMMISSIONI</t>
+  </si>
+  <si>
+    <t>MESE APRILE</t>
+  </si>
+  <si>
+    <t>COBRAL</t>
+  </si>
+  <si>
+    <t>DROPDOWN AGENTI</t>
+  </si>
+  <si>
+    <t>CALCOLO PROVVIGIONE AGENTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOME AGENTE </t>
+  </si>
+  <si>
+    <t>Commissione.Agente</t>
+  </si>
+  <si>
+    <t>FILTRI</t>
+  </si>
+  <si>
+    <t>TOTALE Commissione.Agente</t>
+  </si>
+  <si>
+    <t>seleziona AGENTE</t>
+  </si>
+  <si>
+    <t>MANDATARIO scelto</t>
+  </si>
+  <si>
+    <t>NOME AGENTE scelto</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -173,8 +374,44 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -193,8 +430,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -217,12 +484,239 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -245,6 +739,67 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -261,6 +816,209 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>108857</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1755320</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>94184</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Immagine 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="299357"/>
+          <a:ext cx="15239999" cy="7605327"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2050" name="AutoShape 2" descr="https://lh3.googleusercontent.com/gg-dl/AOI_d___0_UI2n-KJhoDDNmbBkcb2JkExhRCGbtEd8TJfmI3FFkEYH3SshBOFGPG_ZlvH8xidrS46rDjs9V09P9dY-GccOb4sbuJTqTplgju2yCnjLu6OZycCMNSBzVoPLFdd9uCufgoWn7YVmgIC-piG9oal9S16BR1ecCny5zCwUGAommEQg=s1600-rj"/>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="609600" y="9629775"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2051" name="AutoShape 3" descr="https://lh3.googleusercontent.com/gg-dl/AOI_d___0_UI2n-KJhoDDNmbBkcb2JkExhRCGbtEd8TJfmI3FFkEYH3SshBOFGPG_ZlvH8xidrS46rDjs9V09P9dY-GccOb4sbuJTqTplgju2yCnjLu6OZycCMNSBzVoPLFdd9uCufgoWn7YVmgIC-piG9oal9S16BR1ecCny5zCwUGAommEQg=s1600-rj"/>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="609600" y="9058275"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>163286</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>233094</xdr:colOff>
+      <xdr:row>144</xdr:row>
+      <xdr:rowOff>21348</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Immagine 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="20737286"/>
+          <a:ext cx="12710844" cy="6716062"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2095500</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>40821</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>544286</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>175828</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Immagine 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7361464" y="13756821"/>
+          <a:ext cx="8926286" cy="4135507"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -525,8 +1283,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B27"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="149.42578125" customWidth="1"/>
@@ -653,24 +1411,30 @@
       <c r="A22" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="2"/>
+      <c r="B22" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="23" spans="1:2" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A23" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="2"/>
+      <c r="B23" s="2" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="24" spans="1:2" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A24" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
       <c r="B25" s="2"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -683,6 +1447,7 @@
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
     </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A15" r:id="rId1"/>
@@ -690,9 +1455,705 @@
     <hyperlink ref="A17" r:id="rId3"/>
     <hyperlink ref="A18" r:id="rId4"/>
     <hyperlink ref="A21" r:id="rId5"/>
-    <hyperlink ref="B24" r:id="rId6"/>
+    <hyperlink ref="A25" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
+  <legacyDrawing r:id="rId8"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B43:N70"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="21.140625" customWidth="1"/>
+    <col min="3" max="4" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="43" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="34"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="38"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="38"/>
+      <c r="G44" s="38"/>
+      <c r="H44" s="38"/>
+      <c r="I44" s="38"/>
+      <c r="J44" s="38"/>
+      <c r="K44" s="38"/>
+      <c r="L44" s="38"/>
+      <c r="M44" s="38"/>
+      <c r="N44" s="46"/>
+    </row>
+    <row r="45" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="22"/>
+      <c r="C45" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="D45" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E45" s="38"/>
+      <c r="F45" s="38"/>
+      <c r="G45" s="38"/>
+      <c r="H45" s="46"/>
+      <c r="I45" s="38"/>
+      <c r="J45" s="38"/>
+      <c r="K45" s="38"/>
+      <c r="L45" s="38"/>
+      <c r="M45" s="38"/>
+      <c r="N45" s="46" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="49" t="s">
+        <v>51</v>
+      </c>
+      <c r="C46" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D46" s="38"/>
+      <c r="E46" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="F46" s="38"/>
+      <c r="G46" s="38"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="J46" s="16"/>
+      <c r="K46" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="L46" s="16"/>
+      <c r="M46" s="16"/>
+      <c r="N46" s="18"/>
+    </row>
+    <row r="47" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="D47" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="E47" s="54">
+        <f>SUM(E50:E53)</f>
+        <v>606</v>
+      </c>
+      <c r="F47" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="G47" s="54">
+        <f>SUM(F50:F53)</f>
+        <v>4001.5</v>
+      </c>
+      <c r="H47" s="20"/>
+      <c r="I47" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="J47" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="K47" s="54">
+        <f>SUM(K50:K53)</f>
+        <v>2000</v>
+      </c>
+      <c r="L47" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="M47" s="54">
+        <f>SUM(L50:L53)</f>
+        <v>19001.5</v>
+      </c>
+      <c r="N47" s="20"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B48" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="17"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="17"/>
+      <c r="M48" s="17"/>
+      <c r="N48" s="20"/>
+    </row>
+    <row r="49" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B49" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="17"/>
+      <c r="D49" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="E49" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="F49" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="G49" s="28"/>
+      <c r="H49" s="33"/>
+      <c r="I49" s="28"/>
+      <c r="J49" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="K49" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="L49" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="M49" s="28"/>
+      <c r="N49" s="20"/>
+    </row>
+    <row r="50" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B50" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="C50" s="17"/>
+      <c r="D50" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="E50" s="27">
+        <v>100</v>
+      </c>
+      <c r="F50" s="27">
+        <v>500.25</v>
+      </c>
+      <c r="G50" s="28"/>
+      <c r="H50" s="33"/>
+      <c r="I50" s="28"/>
+      <c r="J50" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="K50" s="27">
+        <v>200</v>
+      </c>
+      <c r="L50" s="27">
+        <v>1500.25</v>
+      </c>
+      <c r="M50" s="28"/>
+      <c r="N50" s="20"/>
+    </row>
+    <row r="51" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B51" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="C51" s="17"/>
+      <c r="D51" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="E51" s="27">
+        <v>101</v>
+      </c>
+      <c r="F51" s="27">
+        <v>700.25</v>
+      </c>
+      <c r="G51" s="28"/>
+      <c r="H51" s="33"/>
+      <c r="I51" s="28"/>
+      <c r="J51" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="K51" s="27">
+        <v>300</v>
+      </c>
+      <c r="L51" s="27">
+        <v>3500.25</v>
+      </c>
+      <c r="M51" s="28"/>
+      <c r="N51" s="20"/>
+    </row>
+    <row r="52" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="C52" s="17"/>
+      <c r="D52" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="E52" s="27">
+        <v>102</v>
+      </c>
+      <c r="F52" s="27">
+        <v>800.25</v>
+      </c>
+      <c r="G52" s="28"/>
+      <c r="H52" s="33"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="K52" s="27">
+        <v>500</v>
+      </c>
+      <c r="L52" s="27">
+        <v>4500.25</v>
+      </c>
+      <c r="M52" s="28"/>
+      <c r="N52" s="20"/>
+    </row>
+    <row r="53" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B53" s="22"/>
+      <c r="C53" s="17"/>
+      <c r="D53" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="E53" s="44">
+        <f>SUM(E50:E52)</f>
+        <v>303</v>
+      </c>
+      <c r="F53" s="44">
+        <f>SUM(F50:F52)</f>
+        <v>2000.75</v>
+      </c>
+      <c r="G53" s="28"/>
+      <c r="H53" s="33"/>
+      <c r="I53" s="28"/>
+      <c r="J53" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="K53" s="44">
+        <f>SUM(K50:K52)</f>
+        <v>1000</v>
+      </c>
+      <c r="L53" s="44">
+        <f>SUM(L50:L52)</f>
+        <v>9500.75</v>
+      </c>
+      <c r="M53" s="28"/>
+      <c r="N53" s="20"/>
+    </row>
+    <row r="54" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="22"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="28"/>
+      <c r="E54" s="28"/>
+      <c r="F54" s="28"/>
+      <c r="G54" s="28"/>
+      <c r="H54" s="33"/>
+      <c r="I54" s="28"/>
+      <c r="J54" s="28"/>
+      <c r="K54" s="28"/>
+      <c r="L54" s="28"/>
+      <c r="M54" s="28"/>
+      <c r="N54" s="20"/>
+    </row>
+    <row r="55" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B55" s="22"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="H55" s="33"/>
+      <c r="I55" s="28"/>
+      <c r="J55" s="28"/>
+      <c r="K55" s="28"/>
+      <c r="L55" s="28"/>
+      <c r="M55" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="N55" s="20"/>
+    </row>
+    <row r="56" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="22"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="28"/>
+      <c r="E56" s="28"/>
+      <c r="F56" s="28"/>
+      <c r="G56" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="H56" s="33"/>
+      <c r="I56" s="28"/>
+      <c r="J56" s="28"/>
+      <c r="K56" s="28"/>
+      <c r="L56" s="28"/>
+      <c r="M56" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="N56" s="20"/>
+    </row>
+    <row r="57" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B57" s="19"/>
+      <c r="C57" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="D57" s="58" t="s">
+        <v>47</v>
+      </c>
+      <c r="E57" s="31"/>
+      <c r="F57" s="31"/>
+      <c r="G57" s="38"/>
+      <c r="H57" s="32"/>
+      <c r="I57" s="31"/>
+      <c r="J57" s="31"/>
+      <c r="K57" s="31"/>
+      <c r="L57" s="31"/>
+      <c r="M57" s="38"/>
+      <c r="N57" s="46"/>
+    </row>
+    <row r="58" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="19"/>
+      <c r="C58" s="63" t="s">
+        <v>55</v>
+      </c>
+      <c r="D58" s="30"/>
+      <c r="E58" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="62"/>
+      <c r="I58" s="63" t="s">
+        <v>55</v>
+      </c>
+      <c r="J58" s="30"/>
+      <c r="K58" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="L58" s="30"/>
+      <c r="M58" s="30"/>
+      <c r="N58" s="18"/>
+    </row>
+    <row r="59" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="19"/>
+      <c r="C59" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D59" s="43"/>
+      <c r="E59" s="43"/>
+      <c r="F59" s="28"/>
+      <c r="G59" s="28"/>
+      <c r="H59" s="33"/>
+      <c r="I59" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="J59" s="28"/>
+      <c r="K59" s="43"/>
+      <c r="L59" s="28"/>
+      <c r="M59" s="28"/>
+      <c r="N59" s="20"/>
+    </row>
+    <row r="60" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="19"/>
+      <c r="C60" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="D60" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="E60" s="69" t="s">
+        <v>52</v>
+      </c>
+      <c r="F60" s="70">
+        <f>SUM(G63:G65)</f>
+        <v>50.018750000000004</v>
+      </c>
+      <c r="G60" s="28"/>
+      <c r="H60" s="33"/>
+      <c r="I60" s="67" t="s">
+        <v>42</v>
+      </c>
+      <c r="J60" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="K60" s="69" t="s">
+        <v>52</v>
+      </c>
+      <c r="L60" s="71">
+        <f>SUM(M63:M65)</f>
+        <v>237.51874999999998</v>
+      </c>
+      <c r="M60" s="72"/>
+      <c r="N60" s="20"/>
+    </row>
+    <row r="61" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="19"/>
+      <c r="C61" s="40"/>
+      <c r="D61" s="45"/>
+      <c r="E61" s="45"/>
+      <c r="F61" s="45"/>
+      <c r="G61" s="45"/>
+      <c r="H61" s="60"/>
+      <c r="I61" s="28"/>
+      <c r="N61" s="20"/>
+    </row>
+    <row r="62" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="19"/>
+      <c r="C62" s="57"/>
+      <c r="D62" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="E62" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="F62" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="G62" s="62" t="s">
+        <v>50</v>
+      </c>
+      <c r="H62" s="33"/>
+      <c r="I62" s="28"/>
+      <c r="J62" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="K62" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="L62" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="M62" s="62" t="s">
+        <v>50</v>
+      </c>
+      <c r="N62" s="20"/>
+    </row>
+    <row r="63" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B63" s="19"/>
+      <c r="C63" s="59"/>
+      <c r="D63" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="E63" s="28">
+        <v>100</v>
+      </c>
+      <c r="F63" s="28">
+        <v>500.25</v>
+      </c>
+      <c r="G63" s="33">
+        <f>(F63/40)</f>
+        <v>12.50625</v>
+      </c>
+      <c r="H63" s="33"/>
+      <c r="I63" s="28"/>
+      <c r="J63" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="K63" s="28">
+        <v>200</v>
+      </c>
+      <c r="L63" s="28">
+        <v>1500.25</v>
+      </c>
+      <c r="M63" s="33">
+        <f>(L63/40)</f>
+        <v>37.506250000000001</v>
+      </c>
+      <c r="N63" s="20"/>
+    </row>
+    <row r="64" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B64" s="19"/>
+      <c r="C64" s="19"/>
+      <c r="D64" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="E64" s="28">
+        <v>101</v>
+      </c>
+      <c r="F64" s="28">
+        <v>700.25</v>
+      </c>
+      <c r="G64" s="33">
+        <f t="shared" ref="G64:G65" si="0">(F64/40)</f>
+        <v>17.506250000000001</v>
+      </c>
+      <c r="H64" s="33"/>
+      <c r="I64" s="28"/>
+      <c r="J64" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="K64" s="28">
+        <v>300</v>
+      </c>
+      <c r="L64" s="28">
+        <v>3500.25</v>
+      </c>
+      <c r="M64" s="33">
+        <f t="shared" ref="M64:M65" si="1">(L64/40)</f>
+        <v>87.506249999999994</v>
+      </c>
+      <c r="N64" s="20"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B65" s="19"/>
+      <c r="C65" s="19"/>
+      <c r="D65" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="E65" s="28">
+        <v>102</v>
+      </c>
+      <c r="F65" s="28">
+        <v>800.25</v>
+      </c>
+      <c r="G65" s="33">
+        <f t="shared" si="0"/>
+        <v>20.006250000000001</v>
+      </c>
+      <c r="H65" s="33"/>
+      <c r="I65" s="28"/>
+      <c r="J65" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="K65" s="28">
+        <v>500</v>
+      </c>
+      <c r="L65" s="28">
+        <v>4500.25</v>
+      </c>
+      <c r="M65" s="33">
+        <f t="shared" si="1"/>
+        <v>112.50624999999999</v>
+      </c>
+      <c r="N65" s="20"/>
+    </row>
+    <row r="66" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="19"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="64" t="s">
+        <v>38</v>
+      </c>
+      <c r="E66" s="65">
+        <f>SUM(E63:E65)</f>
+        <v>303</v>
+      </c>
+      <c r="F66" s="65">
+        <f>SUM(F63:F65)</f>
+        <v>2000.75</v>
+      </c>
+      <c r="G66" s="66">
+        <f>SUM(G63:G65)</f>
+        <v>50.018750000000004</v>
+      </c>
+      <c r="H66" s="33"/>
+      <c r="I66" s="17"/>
+      <c r="J66" s="64" t="s">
+        <v>38</v>
+      </c>
+      <c r="K66" s="65">
+        <f>SUM(K63:K65)</f>
+        <v>1000</v>
+      </c>
+      <c r="L66" s="65">
+        <f>SUM(L63:L65)</f>
+        <v>9500.75</v>
+      </c>
+      <c r="M66" s="66">
+        <f>SUM(M63:M65)</f>
+        <v>237.51874999999998</v>
+      </c>
+      <c r="N66" s="20"/>
+    </row>
+    <row r="67" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="19"/>
+      <c r="C67" s="19"/>
+      <c r="D67" s="17"/>
+      <c r="E67" s="17"/>
+      <c r="F67" s="17"/>
+      <c r="G67" s="17"/>
+      <c r="H67" s="20"/>
+      <c r="I67" s="17"/>
+      <c r="J67" s="17"/>
+      <c r="K67" s="17"/>
+      <c r="L67" s="17"/>
+      <c r="M67" s="17"/>
+      <c r="N67" s="20"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B68" s="19"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="17"/>
+      <c r="E68" s="17"/>
+      <c r="F68" s="17"/>
+      <c r="G68" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="H68" s="20"/>
+      <c r="I68" s="17"/>
+      <c r="J68" s="17"/>
+      <c r="K68" s="17"/>
+      <c r="L68" s="17"/>
+      <c r="M68" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="N68" s="20"/>
+    </row>
+    <row r="69" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="19"/>
+      <c r="C69" s="19"/>
+      <c r="D69" s="17"/>
+      <c r="E69" s="17"/>
+      <c r="F69" s="17"/>
+      <c r="G69" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="H69" s="20"/>
+      <c r="I69" s="17"/>
+      <c r="J69" s="17"/>
+      <c r="K69" s="17"/>
+      <c r="L69" s="17"/>
+      <c r="M69" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="N69" s="20"/>
+    </row>
+    <row r="70" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B70" s="24"/>
+      <c r="C70" s="24"/>
+      <c r="D70" s="25"/>
+      <c r="E70" s="25"/>
+      <c r="F70" s="25"/>
+      <c r="G70" s="25"/>
+      <c r="H70" s="26"/>
+      <c r="I70" s="25"/>
+      <c r="J70" s="25"/>
+      <c r="K70" s="25"/>
+      <c r="L70" s="25"/>
+      <c r="M70" s="25"/>
+      <c r="N70" s="26"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>